--- a/data/raw/sales/Week 27/Nexlev/other_channels.xlsx
+++ b/data/raw/sales/Week 27/Nexlev/other_channels.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\sales\Week 27\Nexlev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A02813AD-A844-43F2-A0A3-A2F8BD9EEAE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A142B14-821F-45B9-9941-A3C8AB3B8A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="D2C - Nexlev" sheetId="3" r:id="rId1"/>
@@ -1162,10 +1162,10 @@
         <v>7</v>
       </c>
       <c r="B2" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>9</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>8</v>
       </c>
       <c r="D2" s="10">
         <v>3</v>
@@ -1182,10 +1182,10 @@
         <v>11</v>
       </c>
       <c r="B3" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>13</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>12</v>
       </c>
       <c r="D3" s="10">
         <v>4</v>
@@ -1202,10 +1202,10 @@
         <v>56</v>
       </c>
       <c r="B4" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>57</v>
       </c>
       <c r="D4" s="10">
         <v>2</v>
@@ -1222,10 +1222,10 @@
         <v>220</v>
       </c>
       <c r="B5" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>221</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>222</v>
       </c>
       <c r="D5" s="10">
         <v>3</v>
@@ -1242,10 +1242,10 @@
         <v>17</v>
       </c>
       <c r="B6" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>19</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>18</v>
       </c>
       <c r="D6" s="10">
         <v>2</v>
@@ -1262,10 +1262,10 @@
         <v>95</v>
       </c>
       <c r="B7" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>97</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>96</v>
       </c>
       <c r="D7" s="10">
         <v>1</v>
@@ -1282,10 +1282,10 @@
         <v>20</v>
       </c>
       <c r="B8" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>21</v>
       </c>
       <c r="D8" s="10">
         <v>9</v>
@@ -1302,10 +1302,10 @@
         <v>23</v>
       </c>
       <c r="B9" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>25</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>24</v>
       </c>
       <c r="D9" s="10">
         <v>2</v>
@@ -1322,10 +1322,10 @@
         <v>107</v>
       </c>
       <c r="B10" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="10" t="s">
         <v>109</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>108</v>
       </c>
       <c r="D10" s="10">
         <v>2</v>
@@ -1342,10 +1342,10 @@
         <v>29</v>
       </c>
       <c r="B11" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>31</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>30</v>
       </c>
       <c r="D11" s="10">
         <v>18</v>
@@ -1362,10 +1362,10 @@
         <v>32</v>
       </c>
       <c r="B12" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>34</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>33</v>
       </c>
       <c r="D12" s="10">
         <v>2</v>
@@ -1382,10 +1382,10 @@
         <v>35</v>
       </c>
       <c r="B13" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>37</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>36</v>
       </c>
       <c r="D13" s="10">
         <v>13</v>
@@ -1402,10 +1402,10 @@
         <v>77</v>
       </c>
       <c r="B14" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" s="10" t="s">
         <v>79</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>78</v>
       </c>
       <c r="D14" s="10">
         <v>2</v>
@@ -1422,10 +1422,10 @@
         <v>122</v>
       </c>
       <c r="B15" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C15" s="10" t="s">
         <v>124</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>123</v>
       </c>
       <c r="D15" s="10">
         <v>1</v>
@@ -1442,10 +1442,10 @@
         <v>125</v>
       </c>
       <c r="B16" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C16" s="10" t="s">
         <v>127</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>126</v>
       </c>
       <c r="D16" s="10">
         <v>1</v>
@@ -1462,10 +1462,10 @@
         <v>128</v>
       </c>
       <c r="B17" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="C17" s="10" t="s">
         <v>130</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>129</v>
       </c>
       <c r="D17" s="10">
         <v>3</v>
@@ -1482,10 +1482,10 @@
         <v>38</v>
       </c>
       <c r="B18" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="10" t="s">
         <v>40</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>39</v>
       </c>
       <c r="D18" s="10">
         <v>2</v>
@@ -1502,10 +1502,10 @@
         <v>137</v>
       </c>
       <c r="B19" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C19" s="10" t="s">
         <v>139</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="D19" s="10">
         <v>2</v>
@@ -1522,10 +1522,10 @@
         <v>80</v>
       </c>
       <c r="B20" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" s="10" t="s">
         <v>82</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>81</v>
       </c>
       <c r="D20" s="10">
         <v>2</v>
@@ -1542,10 +1542,10 @@
         <v>44</v>
       </c>
       <c r="B21" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="10" t="s">
         <v>46</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>45</v>
       </c>
       <c r="D21" s="10">
         <v>3</v>
@@ -1562,10 +1562,10 @@
         <v>191</v>
       </c>
       <c r="B22" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="C22" s="10" t="s">
         <v>193</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>192</v>
       </c>
       <c r="D22" s="10">
         <v>2</v>
@@ -1582,10 +1582,10 @@
         <v>223</v>
       </c>
       <c r="B23" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C23" s="10" t="s">
         <v>100</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>99</v>
       </c>
       <c r="D23" s="10">
         <v>1</v>
@@ -1602,10 +1602,10 @@
         <v>224</v>
       </c>
       <c r="B24" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="10" t="s">
         <v>31</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>30</v>
       </c>
       <c r="D24" s="10">
         <v>1</v>
@@ -2472,10 +2472,10 @@
         <v>92</v>
       </c>
       <c r="B2" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" s="18" t="s">
         <v>94</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>93</v>
       </c>
       <c r="D2" s="19">
         <v>3</v>
@@ -2492,10 +2492,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="18" t="s">
         <v>16</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>15</v>
       </c>
       <c r="D3" s="19">
         <v>5</v>
@@ -2512,10 +2512,10 @@
         <v>149</v>
       </c>
       <c r="B4" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C4" s="18" t="s">
         <v>151</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>150</v>
       </c>
       <c r="D4" s="18">
         <v>1</v>
@@ -2532,10 +2532,10 @@
         <v>197</v>
       </c>
       <c r="B5" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="C5" s="18" t="s">
         <v>199</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>198</v>
       </c>
       <c r="D5" s="19">
         <v>3</v>
@@ -2552,10 +2552,10 @@
         <v>74</v>
       </c>
       <c r="B6" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="18" t="s">
         <v>76</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>75</v>
       </c>
       <c r="D6" s="19">
         <v>16</v>
@@ -2572,10 +2572,10 @@
         <v>104</v>
       </c>
       <c r="B7" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" s="18" t="s">
         <v>106</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>105</v>
       </c>
       <c r="D7" s="20">
         <v>2</v>
@@ -2592,10 +2592,10 @@
         <v>26</v>
       </c>
       <c r="B8" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="18" t="s">
         <v>28</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>27</v>
       </c>
       <c r="D8" s="18">
         <v>3</v>
@@ -2612,10 +2612,10 @@
         <v>110</v>
       </c>
       <c r="B9" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9" s="18" t="s">
         <v>112</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>111</v>
       </c>
       <c r="D9" s="18">
         <v>1</v>
@@ -2632,10 +2632,10 @@
         <v>32</v>
       </c>
       <c r="B10" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="18" t="s">
         <v>34</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>33</v>
       </c>
       <c r="D10" s="18">
         <v>1</v>
@@ -2652,10 +2652,10 @@
         <v>225</v>
       </c>
       <c r="B11" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="C11" s="18" t="s">
         <v>226</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>227</v>
       </c>
       <c r="D11" s="18">
         <v>3</v>
@@ -2672,10 +2672,10 @@
         <v>200</v>
       </c>
       <c r="B12" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="C12" s="18" t="s">
         <v>202</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>201</v>
       </c>
       <c r="D12" s="18">
         <v>2</v>
@@ -2692,10 +2692,10 @@
         <v>119</v>
       </c>
       <c r="B13" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" s="18" t="s">
         <v>121</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>120</v>
       </c>
       <c r="D13" s="18">
         <v>4</v>
@@ -2712,10 +2712,10 @@
         <v>77</v>
       </c>
       <c r="B14" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" s="18" t="s">
         <v>79</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>78</v>
       </c>
       <c r="D14" s="18">
         <v>1</v>
@@ -2732,10 +2732,10 @@
         <v>228</v>
       </c>
       <c r="B15" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="C15" s="18" t="s">
         <v>229</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>230</v>
       </c>
       <c r="D15" s="18">
         <v>1</v>
@@ -2752,10 +2752,10 @@
         <v>158</v>
       </c>
       <c r="B16" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="C16" s="18" t="s">
         <v>160</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>159</v>
       </c>
       <c r="D16" s="18">
         <v>1</v>
@@ -2772,10 +2772,10 @@
         <v>125</v>
       </c>
       <c r="B17" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="C17" s="18" t="s">
         <v>127</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>126</v>
       </c>
       <c r="D17" s="18">
         <v>5</v>
@@ -2792,10 +2792,10 @@
         <v>38</v>
       </c>
       <c r="B18" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="18" t="s">
         <v>40</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>39</v>
       </c>
       <c r="D18" s="18">
         <v>5</v>
@@ -2812,10 +2812,10 @@
         <v>164</v>
       </c>
       <c r="B19" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="C19" s="18" t="s">
         <v>166</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>165</v>
       </c>
       <c r="D19" s="18">
         <v>3</v>
@@ -2832,10 +2832,10 @@
         <v>44</v>
       </c>
       <c r="B20" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="18" t="s">
         <v>46</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>45</v>
       </c>
       <c r="D20" s="18">
         <v>2</v>
@@ -2852,10 +2852,10 @@
         <v>167</v>
       </c>
       <c r="B21" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="C21" s="18" t="s">
         <v>169</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>168</v>
       </c>
       <c r="D21" s="18">
         <v>2</v>
@@ -2872,10 +2872,10 @@
         <v>179</v>
       </c>
       <c r="B22" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="C22" s="18" t="s">
         <v>181</v>
-      </c>
-      <c r="C22" s="18" t="s">
-        <v>180</v>
       </c>
       <c r="D22" s="18">
         <v>19</v>
